--- a/耄耋改名_技术方案排期表.xlsx
+++ b/耄耋改名_技术方案排期表.xlsx
@@ -819,27 +819,27 @@
       </c>
       <c r="D4" s="7">
         <f>SUMIF(任务明细!$B$4:$B$48,$A4,任务明细!$E$4:$E$48)</f>
-        <v>13.0</v>
+        <v/>
       </c>
       <c r="E4" s="7">
         <f>SUM($D$4:D4)</f>
-        <v>13.0</v>
+        <v/>
       </c>
       <c r="F4" s="8">
         <f>IF($E$9=0,"",D4/$E$9)</f>
-        <v>0.22807017543859648</v>
+        <v/>
       </c>
       <c r="G4" s="9">
         <f>ROUND(E4*假设与口径!$B$7,0)</f>
-        <v>16.0</v>
+        <v/>
       </c>
       <c r="H4" s="10">
         <f>假设与口径!$B$4</f>
-        <v>46279.0</v>
+        <v/>
       </c>
       <c r="I4" s="10">
         <f>假设与口径!$B$4+$G4-1</f>
-        <v>46294.0</v>
+        <v/>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
@@ -851,13 +851,13 @@
           <t>可命令行验证的改名内核；引擎单测覆盖率 ≥ 90%</t>
         </is>
       </c>
-      <c r="L4" s="11" t="str">
+      <c r="L4" s="11">
         <f>IF(COUNTIF(任务明细!$B$4:$B$48,$A4)=0,"未开始",IF(COUNTIFS(任务明细!$B$4:$B$48,$A4,任务明细!$H$4:$H$48,"已完成")=COUNTIF(任务明细!$B$4:$B$48,$A4),"已完成",IF(COUNTIFS(任务明细!$B$4:$B$48,$A4,任务明细!$H$4:$H$48,"未开始")=COUNTIF(任务明细!$B$4:$B$48,$A4),"未开始","进行中")))</f>
-        <v>未开始</v>
-      </c>
-      <c r="M4" s="11" t="str">
+        <v/>
+      </c>
+      <c r="M4" s="11">
         <f>REPT("█",MAX(1,ROUND($D4/MAX($D$4:$D$8)*18,0)))</f>
-        <v>████████████████</v>
+        <v/>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
@@ -878,27 +878,27 @@
       </c>
       <c r="D5" s="7">
         <f>SUMIF(任务明细!$B$4:$B$48,$A5,任务明细!$E$4:$E$48)</f>
-        <v>14.5</v>
+        <v/>
       </c>
       <c r="E5" s="7">
         <f>SUM($D$4:D5)</f>
-        <v>27.5</v>
+        <v/>
       </c>
       <c r="F5" s="8">
         <f>IF($E$9=0,"",D5/$E$9)</f>
-        <v>0.2543859649122807</v>
+        <v/>
       </c>
       <c r="G5" s="9">
         <f>ROUND(E5*假设与口径!$B$7,0)</f>
-        <v>33.0</v>
+        <v/>
       </c>
       <c r="H5" s="10">
         <f>I4+1</f>
-        <v>46295.0</v>
+        <v/>
       </c>
       <c r="I5" s="10">
         <f>假设与口径!$B$4+$G5-1</f>
-        <v>46311.0</v>
+        <v/>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
@@ -910,13 +910,13 @@
           <t>能用的界面（无形象），可完成一次完整改名</t>
         </is>
       </c>
-      <c r="L5" s="11" t="str">
+      <c r="L5" s="11">
         <f>IF(COUNTIF(任务明细!$B$4:$B$48,$A5)=0,"未开始",IF(COUNTIFS(任务明细!$B$4:$B$48,$A5,任务明细!$H$4:$H$48,"已完成")=COUNTIF(任务明细!$B$4:$B$48,$A5),"已完成",IF(COUNTIFS(任务明细!$B$4:$B$48,$A5,任务明细!$H$4:$H$48,"未开始")=COUNTIF(任务明细!$B$4:$B$48,$A5),"未开始","进行中")))</f>
-        <v>未开始</v>
-      </c>
-      <c r="M5" s="11" t="str">
+        <v/>
+      </c>
+      <c r="M5" s="11">
         <f>REPT("█",MAX(1,ROUND($D5/MAX($D$4:$D$8)*18,0)))</f>
-        <v>██████████████████</v>
+        <v/>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
@@ -937,27 +937,27 @@
       </c>
       <c r="D6" s="7">
         <f>SUMIF(任务明细!$B$4:$B$48,$A6,任务明细!$E$4:$E$48)</f>
-        <v>9.0</v>
+        <v/>
       </c>
       <c r="E6" s="7">
         <f>SUM($D$4:D6)</f>
-        <v>36.5</v>
+        <v/>
       </c>
       <c r="F6" s="8">
         <f>IF($E$9=0,"",D6/$E$9)</f>
-        <v>0.15789473684210525</v>
+        <v/>
       </c>
       <c r="G6" s="9">
         <f>ROUND(E6*假设与口径!$B$7,0)</f>
-        <v>44.0</v>
+        <v/>
       </c>
       <c r="H6" s="10">
         <f>I5+1</f>
-        <v>46312.0</v>
+        <v/>
       </c>
       <c r="I6" s="10">
         <f>假设与口径!$B$4+$G6-1</f>
-        <v>46322.0</v>
+        <v/>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
@@ -969,13 +969,13 @@
           <t>有灵魂的 UI；动作歧义自查通过</t>
         </is>
       </c>
-      <c r="L6" s="11" t="str">
+      <c r="L6" s="11">
         <f>IF(COUNTIF(任务明细!$B$4:$B$48,$A6)=0,"未开始",IF(COUNTIFS(任务明细!$B$4:$B$48,$A6,任务明细!$H$4:$H$48,"已完成")=COUNTIF(任务明细!$B$4:$B$48,$A6),"已完成",IF(COUNTIFS(任务明细!$B$4:$B$48,$A6,任务明细!$H$4:$H$48,"未开始")=COUNTIF(任务明细!$B$4:$B$48,$A6),"未开始","进行中")))</f>
-        <v>未开始</v>
-      </c>
-      <c r="M6" s="11" t="str">
+        <v/>
+      </c>
+      <c r="M6" s="11">
         <f>REPT("█",MAX(1,ROUND($D6/MAX($D$4:$D$8)*18,0)))</f>
-        <v>███████████</v>
+        <v/>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
@@ -996,27 +996,27 @@
       </c>
       <c r="D7" s="7">
         <f>SUMIF(任务明细!$B$4:$B$48,$A7,任务明细!$E$4:$E$48)</f>
-        <v>13.5</v>
+        <v/>
       </c>
       <c r="E7" s="7">
         <f>SUM($D$4:D7)</f>
-        <v>50.0</v>
+        <v/>
       </c>
       <c r="F7" s="8">
         <f>IF($E$9=0,"",D7/$E$9)</f>
-        <v>0.23684210526315788</v>
+        <v/>
       </c>
       <c r="G7" s="9">
         <f>ROUND(E7*假设与口径!$B$7,0)</f>
-        <v>60.0</v>
+        <v/>
       </c>
       <c r="H7" s="10">
         <f>I6+1</f>
-        <v>46323.0</v>
+        <v/>
       </c>
       <c r="I7" s="10">
         <f>假设与口径!$B$4+$G7-1</f>
-        <v>46338.0</v>
+        <v/>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
@@ -1028,13 +1028,13 @@
           <t>安全完整版；TC-07 冲突不覆盖可验证</t>
         </is>
       </c>
-      <c r="L7" s="11" t="str">
+      <c r="L7" s="11">
         <f>IF(COUNTIF(任务明细!$B$4:$B$48,$A7)=0,"未开始",IF(COUNTIFS(任务明细!$B$4:$B$48,$A7,任务明细!$H$4:$H$48,"已完成")=COUNTIF(任务明细!$B$4:$B$48,$A7),"已完成",IF(COUNTIFS(任务明细!$B$4:$B$48,$A7,任务明细!$H$4:$H$48,"未开始")=COUNTIF(任务明细!$B$4:$B$48,$A7),"未开始","进行中")))</f>
-        <v>未开始</v>
-      </c>
-      <c r="M7" s="11" t="str">
+        <v/>
+      </c>
+      <c r="M7" s="11">
         <f>REPT("█",MAX(1,ROUND($D7/MAX($D$4:$D$8)*18,0)))</f>
-        <v>█████████████████</v>
+        <v/>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
@@ -1055,27 +1055,27 @@
       </c>
       <c r="D8" s="7">
         <f>SUMIF(任务明细!$B$4:$B$48,$A8,任务明细!$E$4:$E$48)</f>
-        <v>7.0</v>
+        <v/>
       </c>
       <c r="E8" s="7">
         <f>SUM($D$4:D8)</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="F8" s="8">
         <f>IF($E$9=0,"",D8/$E$9)</f>
-        <v>0.12280701754385964</v>
+        <v/>
       </c>
       <c r="G8" s="9">
         <f>ROUND(E8*假设与口径!$B$7,0)</f>
-        <v>68.0</v>
+        <v/>
       </c>
       <c r="H8" s="10">
         <f>I7+1</f>
-        <v>46339.0</v>
+        <v/>
       </c>
       <c r="I8" s="10">
         <f>假设与口径!$B$4+$G8-1</f>
-        <v>46346.0</v>
+        <v/>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
           <t>可安装的 exe（安装包实测体积已记录）</t>
         </is>
       </c>
-      <c r="L8" s="11" t="str">
+      <c r="L8" s="11">
         <f>IF(COUNTIF(任务明细!$B$4:$B$48,$A8)=0,"未开始",IF(COUNTIFS(任务明细!$B$4:$B$48,$A8,任务明细!$H$4:$H$48,"已完成")=COUNTIF(任务明细!$B$4:$B$48,$A8),"已完成",IF(COUNTIFS(任务明细!$B$4:$B$48,$A8,任务明细!$H$4:$H$48,"未开始")=COUNTIF(任务明细!$B$4:$B$48,$A8),"未开始","进行中")))</f>
-        <v>未开始</v>
-      </c>
-      <c r="M8" s="11" t="str">
+        <v/>
+      </c>
+      <c r="M8" s="11">
         <f>REPT("█",MAX(1,ROUND($D8/MAX($D$4:$D$8)*18,0)))</f>
-        <v>█████████</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1110,24 +1110,24 @@
       </c>
       <c r="D9" s="15">
         <f>SUM(D4:D8)</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="E9" s="15">
         <f>E8</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="F9" s="16">
         <f>IF($E$9=0,"",SUM(F4:F8))</f>
-        <v>1.0</v>
+        <v/>
       </c>
       <c r="G9" s="17">
         <f>G8</f>
-        <v>68.0</v>
+        <v/>
       </c>
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="18">
         <f>I8</f>
-        <v>46346.0</v>
+        <v/>
       </c>
       <c r="J9" s="13" t="n"/>
       <c r="K9" s="13" t="n"/>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B12" s="20">
         <f>SUM(任务明细!$E$4:$E$48)</f>
-        <v>57.0</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B13" s="20">
         <f>SUMIF(任务明细!$H$4:$H$48,"已完成",任务明细!$E$4:$E$48)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B14" s="21">
         <f>IF($B$12=0,"",$B$13/$B$12)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B15" s="22">
         <f>假设与口径!$B$4+ROUND($B$12*假设与口径!$B$7,0)-1</f>
-        <v>46346.0</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B16" s="22">
         <f>假设与口径!$B$4+ROUND($B$12*假设与口径!$B$7*假设与口径!$B$8,0)-1</f>
-        <v>46360.0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1335,16 +1335,16 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I4" s="27">
         <f>SUM($E$4:E4)</f>
-        <v>1.0</v>
+        <v/>
       </c>
       <c r="J4" s="28">
         <f>假设与口径!$B$4+ROUND(I4*假设与口径!$B$7,0)-1</f>
-        <v>46279.0</v>
+        <v/>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
       </c>
       <c r="H5" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I5" s="27">
         <f>SUM($E$4:E5)</f>
-        <v>1.5</v>
+        <v/>
       </c>
       <c r="J5" s="28">
         <f>假设与口径!$B$4+ROUND(I5*假设与口径!$B$7,0)-1</f>
-        <v>46280.0</v>
+        <v/>
       </c>
       <c r="K5" s="6" t="inlineStr"/>
     </row>
@@ -1437,16 +1437,16 @@
       </c>
       <c r="H6" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I6" s="27">
         <f>SUM($E$4:E6)</f>
-        <v>2.5</v>
+        <v/>
       </c>
       <c r="J6" s="28">
         <f>假设与口径!$B$4+ROUND(I6*假设与口径!$B$7,0)-1</f>
-        <v>46281.0</v>
+        <v/>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -1490,16 +1490,16 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I7" s="27">
         <f>SUM($E$4:E7)</f>
-        <v>4.5</v>
+        <v/>
       </c>
       <c r="J7" s="28">
         <f>假设与口径!$B$4+ROUND(I7*假设与口径!$B$7,0)-1</f>
-        <v>46283.0</v>
+        <v/>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -1543,16 +1543,16 @@
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I8" s="27">
         <f>SUM($E$4:E8)</f>
-        <v>5.0</v>
+        <v/>
       </c>
       <c r="J8" s="28">
         <f>假设与口径!$B$4+ROUND(I8*假设与口径!$B$7,0)-1</f>
-        <v>46284.0</v>
+        <v/>
       </c>
       <c r="K8" s="6" t="inlineStr"/>
     </row>
@@ -1592,16 +1592,16 @@
       </c>
       <c r="H9" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I9" s="27">
         <f>SUM($E$4:E9)</f>
-        <v>5.5</v>
+        <v/>
       </c>
       <c r="J9" s="28">
         <f>假设与口径!$B$4+ROUND(I9*假设与口径!$B$7,0)-1</f>
-        <v>46285.0</v>
+        <v/>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
@@ -1645,16 +1645,16 @@
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I10" s="27">
         <f>SUM($E$4:E10)</f>
-        <v>7.0</v>
+        <v/>
       </c>
       <c r="J10" s="28">
         <f>假设与口径!$B$4+ROUND(I10*假设与口径!$B$7,0)-1</f>
-        <v>46286.0</v>
+        <v/>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I11" s="27">
         <f>SUM($E$4:E11)</f>
-        <v>9.5</v>
+        <v/>
       </c>
       <c r="J11" s="28">
         <f>假设与口径!$B$4+ROUND(I11*假设与口径!$B$7,0)-1</f>
-        <v>46289.0</v>
+        <v/>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -1751,16 +1751,16 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I12" s="27">
         <f>SUM($E$4:E12)</f>
-        <v>11.0</v>
+        <v/>
       </c>
       <c r="J12" s="28">
         <f>假设与口径!$B$4+ROUND(I12*假设与口径!$B$7,0)-1</f>
-        <v>46291.0</v>
+        <v/>
       </c>
       <c r="K12" s="6" t="inlineStr"/>
     </row>
@@ -1800,16 +1800,16 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I13" s="27">
         <f>SUM($E$4:E13)</f>
-        <v>12.0</v>
+        <v/>
       </c>
       <c r="J13" s="28">
         <f>假设与口径!$B$4+ROUND(I13*假设与口径!$B$7,0)-1</f>
-        <v>46292.0</v>
+        <v/>
       </c>
       <c r="K13" s="6" t="inlineStr"/>
     </row>
@@ -1849,16 +1849,16 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I14" s="27">
         <f>SUM($E$4:E14)</f>
-        <v>13.0</v>
+        <v/>
       </c>
       <c r="J14" s="28">
         <f>假设与口径!$B$4+ROUND(I14*假设与口径!$B$7,0)-1</f>
-        <v>46294.0</v>
+        <v/>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -1902,16 +1902,16 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I15" s="27">
         <f>SUM($E$4:E15)</f>
-        <v>13.5</v>
+        <v/>
       </c>
       <c r="J15" s="28">
         <f>假设与口径!$B$4+ROUND(I15*假设与口径!$B$7,0)-1</f>
-        <v>46294.0</v>
+        <v/>
       </c>
       <c r="K15" s="6" t="inlineStr"/>
     </row>
@@ -1951,16 +1951,16 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I16" s="27">
         <f>SUM($E$4:E16)</f>
-        <v>15.5</v>
+        <v/>
       </c>
       <c r="J16" s="28">
         <f>假设与口径!$B$4+ROUND(I16*假设与口径!$B$7,0)-1</f>
-        <v>46297.0</v>
+        <v/>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I17" s="27">
         <f>SUM($E$4:E17)</f>
-        <v>16.5</v>
+        <v/>
       </c>
       <c r="J17" s="28">
         <f>假设与口径!$B$4+ROUND(I17*假设与口径!$B$7,0)-1</f>
-        <v>46298.0</v>
+        <v/>
       </c>
       <c r="K17" s="6" t="inlineStr"/>
     </row>
@@ -2053,16 +2053,16 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I18" s="27">
         <f>SUM($E$4:E18)</f>
-        <v>18.5</v>
+        <v/>
       </c>
       <c r="J18" s="28">
         <f>假设与口径!$B$4+ROUND(I18*假设与口径!$B$7,0)-1</f>
-        <v>46300.0</v>
+        <v/>
       </c>
       <c r="K18" s="6" t="inlineStr"/>
     </row>
@@ -2102,16 +2102,16 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I19" s="27">
         <f>SUM($E$4:E19)</f>
-        <v>19.5</v>
+        <v/>
       </c>
       <c r="J19" s="28">
         <f>假设与口径!$B$4+ROUND(I19*假设与口径!$B$7,0)-1</f>
-        <v>46301.0</v>
+        <v/>
       </c>
       <c r="K19" s="6" t="inlineStr"/>
     </row>
@@ -2151,16 +2151,16 @@
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I20" s="27">
         <f>SUM($E$4:E20)</f>
-        <v>22.0</v>
+        <v/>
       </c>
       <c r="J20" s="28">
         <f>假设与口径!$B$4+ROUND(I20*假设与口径!$B$7,0)-1</f>
-        <v>46304.0</v>
+        <v/>
       </c>
       <c r="K20" s="6" t="inlineStr"/>
     </row>
@@ -2200,16 +2200,16 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I21" s="27">
         <f>SUM($E$4:E21)</f>
-        <v>23.5</v>
+        <v/>
       </c>
       <c r="J21" s="28">
         <f>假设与口径!$B$4+ROUND(I21*假设与口径!$B$7,0)-1</f>
-        <v>46306.0</v>
+        <v/>
       </c>
       <c r="K21" s="6" t="inlineStr"/>
     </row>
@@ -2249,16 +2249,16 @@
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I22" s="27">
         <f>SUM($E$4:E22)</f>
-        <v>25.0</v>
+        <v/>
       </c>
       <c r="J22" s="28">
         <f>假设与口径!$B$4+ROUND(I22*假设与口径!$B$7,0)-1</f>
-        <v>46308.0</v>
+        <v/>
       </c>
       <c r="K22" s="6" t="inlineStr"/>
     </row>
@@ -2298,16 +2298,16 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I23" s="27">
         <f>SUM($E$4:E23)</f>
-        <v>26.0</v>
+        <v/>
       </c>
       <c r="J23" s="28">
         <f>假设与口径!$B$4+ROUND(I23*假设与口径!$B$7,0)-1</f>
-        <v>46309.0</v>
+        <v/>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
     </row>
@@ -2347,16 +2347,16 @@
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I24" s="27">
         <f>SUM($E$4:E24)</f>
-        <v>26.5</v>
+        <v/>
       </c>
       <c r="J24" s="28">
         <f>假设与口径!$B$4+ROUND(I24*假设与口径!$B$7,0)-1</f>
-        <v>46310.0</v>
+        <v/>
       </c>
       <c r="K24" s="6" t="inlineStr"/>
     </row>
@@ -2396,16 +2396,16 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I25" s="27">
         <f>SUM($E$4:E25)</f>
-        <v>27.5</v>
+        <v/>
       </c>
       <c r="J25" s="28">
         <f>假设与口径!$B$4+ROUND(I25*假设与口径!$B$7,0)-1</f>
-        <v>46311.0</v>
+        <v/>
       </c>
       <c r="K25" s="6" t="inlineStr"/>
     </row>
@@ -2445,16 +2445,16 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I26" s="27">
         <f>SUM($E$4:E26)</f>
-        <v>29.0</v>
+        <v/>
       </c>
       <c r="J26" s="28">
         <f>假设与口径!$B$4+ROUND(I26*假设与口径!$B$7,0)-1</f>
-        <v>46313.0</v>
+        <v/>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
@@ -2498,16 +2498,16 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I27" s="27">
         <f>SUM($E$4:E27)</f>
-        <v>30.5</v>
+        <v/>
       </c>
       <c r="J27" s="28">
         <f>假设与口径!$B$4+ROUND(I27*假设与口径!$B$7,0)-1</f>
-        <v>46315.0</v>
+        <v/>
       </c>
       <c r="K27" s="6" t="inlineStr"/>
     </row>
@@ -2547,16 +2547,16 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I28" s="27">
         <f>SUM($E$4:E28)</f>
-        <v>32.5</v>
+        <v/>
       </c>
       <c r="J28" s="28">
         <f>假设与口径!$B$4+ROUND(I28*假设与口径!$B$7,0)-1</f>
-        <v>46317.0</v>
+        <v/>
       </c>
       <c r="K28" s="6" t="inlineStr"/>
     </row>
@@ -2596,16 +2596,16 @@
       </c>
       <c r="H29" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I29" s="27">
         <f>SUM($E$4:E29)</f>
-        <v>35.5</v>
+        <v/>
       </c>
       <c r="J29" s="28">
         <f>假设与口径!$B$4+ROUND(I29*假设与口径!$B$7,0)-1</f>
-        <v>46321.0</v>
+        <v/>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
@@ -2649,16 +2649,16 @@
       </c>
       <c r="H30" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I30" s="27">
         <f>SUM($E$4:E30)</f>
-        <v>36.0</v>
+        <v/>
       </c>
       <c r="J30" s="28">
         <f>假设与口径!$B$4+ROUND(I30*假设与口径!$B$7,0)-1</f>
-        <v>46321.0</v>
+        <v/>
       </c>
       <c r="K30" s="6" t="inlineStr"/>
     </row>
@@ -2698,16 +2698,16 @@
       </c>
       <c r="H31" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I31" s="27">
         <f>SUM($E$4:E31)</f>
-        <v>36.5</v>
+        <v/>
       </c>
       <c r="J31" s="28">
         <f>假设与口径!$B$4+ROUND(I31*假设与口径!$B$7,0)-1</f>
-        <v>46322.0</v>
+        <v/>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I32" s="27">
         <f>SUM($E$4:E32)</f>
-        <v>37.0</v>
+        <v/>
       </c>
       <c r="J32" s="28">
         <f>假设与口径!$B$4+ROUND(I32*假设与口径!$B$7,0)-1</f>
-        <v>46322.0</v>
+        <v/>
       </c>
       <c r="K32" s="6" t="inlineStr"/>
     </row>
@@ -2800,16 +2800,16 @@
       </c>
       <c r="H33" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I33" s="27">
         <f>SUM($E$4:E33)</f>
-        <v>38.5</v>
+        <v/>
       </c>
       <c r="J33" s="28">
         <f>假设与口径!$B$4+ROUND(I33*假设与口径!$B$7,0)-1</f>
-        <v>46324.0</v>
+        <v/>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
@@ -2853,16 +2853,16 @@
       </c>
       <c r="H34" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I34" s="27">
         <f>SUM($E$4:E34)</f>
-        <v>40.0</v>
+        <v/>
       </c>
       <c r="J34" s="28">
         <f>假设与口径!$B$4+ROUND(I34*假设与口径!$B$7,0)-1</f>
-        <v>46326.0</v>
+        <v/>
       </c>
       <c r="K34" s="6" t="inlineStr"/>
     </row>
@@ -2902,16 +2902,16 @@
       </c>
       <c r="H35" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I35" s="27">
         <f>SUM($E$4:E35)</f>
-        <v>42.0</v>
+        <v/>
       </c>
       <c r="J35" s="28">
         <f>假设与口径!$B$4+ROUND(I35*假设与口径!$B$7,0)-1</f>
-        <v>46328.0</v>
+        <v/>
       </c>
       <c r="K35" s="6" t="inlineStr"/>
     </row>
@@ -2951,16 +2951,16 @@
       </c>
       <c r="H36" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I36" s="27">
         <f>SUM($E$4:E36)</f>
-        <v>43.5</v>
+        <v/>
       </c>
       <c r="J36" s="28">
         <f>假设与口径!$B$4+ROUND(I36*假设与口径!$B$7,0)-1</f>
-        <v>46330.0</v>
+        <v/>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
@@ -3004,16 +3004,16 @@
       </c>
       <c r="H37" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I37" s="27">
         <f>SUM($E$4:E37)</f>
-        <v>44.5</v>
+        <v/>
       </c>
       <c r="J37" s="28">
         <f>假设与口径!$B$4+ROUND(I37*假设与口径!$B$7,0)-1</f>
-        <v>46331.0</v>
+        <v/>
       </c>
       <c r="K37" s="6" t="inlineStr"/>
     </row>
@@ -3053,16 +3053,16 @@
       </c>
       <c r="H38" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I38" s="27">
         <f>SUM($E$4:E38)</f>
-        <v>45.5</v>
+        <v/>
       </c>
       <c r="J38" s="28">
         <f>假设与口径!$B$4+ROUND(I38*假设与口径!$B$7,0)-1</f>
-        <v>46333.0</v>
+        <v/>
       </c>
       <c r="K38" s="6" t="inlineStr"/>
     </row>
@@ -3102,16 +3102,16 @@
       </c>
       <c r="H39" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I39" s="27">
         <f>SUM($E$4:E39)</f>
-        <v>47.5</v>
+        <v/>
       </c>
       <c r="J39" s="28">
         <f>假设与口径!$B$4+ROUND(I39*假设与口径!$B$7,0)-1</f>
-        <v>46335.0</v>
+        <v/>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
@@ -3155,16 +3155,16 @@
       </c>
       <c r="H40" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I40" s="27">
         <f>SUM($E$4:E40)</f>
-        <v>49.0</v>
+        <v/>
       </c>
       <c r="J40" s="28">
         <f>假设与口径!$B$4+ROUND(I40*假设与口径!$B$7,0)-1</f>
-        <v>46337.0</v>
+        <v/>
       </c>
       <c r="K40" s="6" t="inlineStr"/>
     </row>
@@ -3204,16 +3204,16 @@
       </c>
       <c r="H41" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I41" s="27">
         <f>SUM($E$4:E41)</f>
-        <v>50.0</v>
+        <v/>
       </c>
       <c r="J41" s="28">
         <f>假设与口径!$B$4+ROUND(I41*假设与口径!$B$7,0)-1</f>
-        <v>46338.0</v>
+        <v/>
       </c>
       <c r="K41" s="6" t="inlineStr"/>
     </row>
@@ -3253,16 +3253,16 @@
       </c>
       <c r="H42" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I42" s="27">
         <f>SUM($E$4:E42)</f>
-        <v>51.0</v>
+        <v/>
       </c>
       <c r="J42" s="28">
         <f>假设与口径!$B$4+ROUND(I42*假设与口径!$B$7,0)-1</f>
-        <v>46339.0</v>
+        <v/>
       </c>
       <c r="K42" s="6" t="inlineStr"/>
     </row>
@@ -3302,16 +3302,16 @@
       </c>
       <c r="H43" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I43" s="27">
         <f>SUM($E$4:E43)</f>
-        <v>51.5</v>
+        <v/>
       </c>
       <c r="J43" s="28">
         <f>假设与口径!$B$4+ROUND(I43*假设与口径!$B$7,0)-1</f>
-        <v>46340.0</v>
+        <v/>
       </c>
       <c r="K43" s="6" t="inlineStr"/>
     </row>
@@ -3351,16 +3351,16 @@
       </c>
       <c r="H44" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="I44" s="27">
         <f>SUM($E$4:E44)</f>
-        <v>52.5</v>
+        <v/>
       </c>
       <c r="J44" s="28">
         <f>假设与口径!$B$4+ROUND(I44*假设与口径!$B$7,0)-1</f>
-        <v>46341.0</v>
+        <v/>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
@@ -3409,11 +3409,11 @@
       </c>
       <c r="I45" s="27">
         <f>SUM($E$4:E45)</f>
-        <v>53.0</v>
+        <v/>
       </c>
       <c r="J45" s="28">
         <f>假设与口径!$B$4+ROUND(I45*假设与口径!$B$7,0)-1</f>
-        <v>46342.0</v>
+        <v/>
       </c>
       <c r="K45" s="6" t="inlineStr"/>
     </row>
@@ -3458,11 +3458,11 @@
       </c>
       <c r="I46" s="27">
         <f>SUM($E$4:E46)</f>
-        <v>55.0</v>
+        <v/>
       </c>
       <c r="J46" s="28">
         <f>假设与口径!$B$4+ROUND(I46*假设与口径!$B$7,0)-1</f>
-        <v>46344.0</v>
+        <v/>
       </c>
       <c r="K46" s="6" t="inlineStr"/>
     </row>
@@ -3502,16 +3502,16 @@
       </c>
       <c r="H47" s="26" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="I47" s="27">
         <f>SUM($E$4:E47)</f>
-        <v>56.0</v>
+        <v/>
       </c>
       <c r="J47" s="28">
         <f>假设与口径!$B$4+ROUND(I47*假设与口径!$B$7,0)-1</f>
-        <v>46345.0</v>
+        <v/>
       </c>
       <c r="K47" s="6" t="inlineStr"/>
     </row>
@@ -3556,11 +3556,11 @@
       </c>
       <c r="I48" s="27">
         <f>SUM($E$4:E48)</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="J48" s="28">
         <f>假设与口径!$B$4+ROUND(I48*假设与口径!$B$7,0)-1</f>
-        <v>46346.0</v>
+        <v/>
       </c>
       <c r="K48" s="6" t="inlineStr"/>
     </row>
@@ -3579,18 +3579,18 @@
       <c r="D49" s="12" t="n"/>
       <c r="E49" s="29">
         <f>SUM(E4:E48)</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="12" t="n"/>
       <c r="H49" s="12" t="n"/>
       <c r="I49" s="29">
         <f>I48</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="J49" s="30">
         <f>J48</f>
-        <v>46346.0</v>
+        <v/>
       </c>
       <c r="K49" s="12" t="n"/>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F3" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F4" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="F5" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="F6" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F7" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="F8" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F9" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F10" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="F11" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="F12" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="F13" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F14" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="F15" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F16" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="F17" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F19" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F20" s="26" t="inlineStr">
         <is>
-          <t>未通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B7" s="36">
         <f>B6/B5</f>
-        <v>1.2</v>
+        <v/>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B10" s="20">
         <f>SUM(任务明细!$E$4:$E$48)</f>
-        <v>57.0</v>
+        <v/>
       </c>
       <c r="C10" s="37" t="n"/>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="B11" s="38">
         <f>ROUND(B10*B7,0)</f>
-        <v>68.0</v>
+        <v/>
       </c>
       <c r="C11" s="37" t="n"/>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B12" s="22">
         <f>B4+B11-1</f>
-        <v>46346.0</v>
+        <v/>
       </c>
       <c r="C12" s="37" t="n"/>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B13" s="22">
         <f>B4+ROUND(B10*B7*B8,0)-1</f>
-        <v>46360.0</v>
+        <v/>
       </c>
       <c r="C13" s="37" t="n"/>
     </row>
@@ -4715,13 +4715,13 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
